--- a/Catalogo de Dados.xlsx
+++ b/Catalogo de Dados.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Saeb Estado 2023" sheetId="1" r:id="rId1"/>
+    <sheet name="Censo IBGE" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Saeb Estado 2023'!$A$1:$E$1</definedName>
@@ -99,8 +100,91 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Autor</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Autor:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Tipo de dado (texto, número inteiro, decimal, data, booleano) de cada campo
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Autor:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+para numéricos, os valores mínimos e máximos esperados; para categóricos, as categorias possíveis. Essa informação pode vim na descrição do campo</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Autor:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+ de qual fonte o dado veio e se houve alguma transformação ou junção para compô-lo. Essa informação pode vim na descrição do campo ou exibido de forma diagramável (Databricks auxilia nesse aspecto).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="249">
   <si>
     <t>Nome</t>
   </si>
@@ -582,9 +666,6 @@
     <t>Num</t>
   </si>
   <si>
-    <t>Char</t>
-  </si>
-  <si>
     <t>Localização da escola</t>
   </si>
   <si>
@@ -787,12 +868,78 @@
   </si>
   <si>
     <t>Microdados Saeb 2023</t>
+  </si>
+  <si>
+    <t>ANO</t>
+  </si>
+  <si>
+    <t>UFN</t>
+  </si>
+  <si>
+    <t>E_ANOSESTUDO</t>
+  </si>
+  <si>
+    <t>GINI</t>
+  </si>
+  <si>
+    <t>RDPC</t>
+  </si>
+  <si>
+    <t>IDHM</t>
+  </si>
+  <si>
+    <t>IDHM_E</t>
+  </si>
+  <si>
+    <t>IDHM_L</t>
+  </si>
+  <si>
+    <t>IDHM_R</t>
+  </si>
+  <si>
+    <t>Ano de realização do censo</t>
+  </si>
+  <si>
+    <t>Nome do Estado da Federação</t>
+  </si>
+  <si>
+    <t>Número médio de anos de estudo que uma geração de crianças que ingressa na escola deverá completar ao atingir 18 anos de idade, se os padrões atuais se mantiverem ao longo de sua vida escolar.</t>
+  </si>
+  <si>
+    <t>Indice de Gini. Mede o grau de desigualdade existente na distribuição de indivíduos segundo a renda domiciliar per capita. Seu valor varia de 0, quando não há desigualdade (a renda domiciliar per capita de todos os indivíduos tem o mesmo valor), a 1, quando a desigualdade é máxima (apenas um indivíduo detém toda a renda).O universo de indivíduos é limitado àqueles que vivem em domicílios particulares permanentes.</t>
+  </si>
+  <si>
+    <t>0 a 1</t>
+  </si>
+  <si>
+    <t>Renda Per Capta Média. Razão entre o somatório da renda de todos os indivíduos residentes em domicílios particulares permanentes e o número total desses indivíduos. Valores em reais de 01/agosto de 2010.</t>
+  </si>
+  <si>
+    <t>Índice de Desenvolvimento Humano Municipal. Média geométrica dos índices das dimensões Renda, Educação e Longevidade, com pesos iguais.</t>
+  </si>
+  <si>
+    <t>Índice sintético da dimensão Educação que é um dos 3 componentes do IDHM. É obtido através da média geométrica do subíndice de frequência de crianças e jovens à escola, com peso de 2/3, e do subíndice de escolaridade da população adulta, com peso de 1/3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Índice da dimensão Longevidade que é um dos 3 componentes do IDHM. É obtido a partir do indicador Esperança de vida ao nascer, através da fórmula: [(valor observado do indicador) - (valor mínimo)] / [(valor máximo) - (valor mínimo)], onde os valores mínimo e máximo são 25 e 85 anos, respectivamente. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Índice da dimensão Renda que é um dos 3 componentes do IDHM. É obtido a partir do indicador Renda per capita, através da fórmula: [ln (valor observado do indicador) - ln (valor mínimo)] / [ln (valor máximo) - ln (valor mínimo)], onde os valores mínimo e máximo são R$ 8,00 e R$ 4.033,00 (a preços de agosto de 2010). </t>
+  </si>
+  <si>
+    <t>Censo IBGE 2010</t>
+  </si>
+  <si>
+    <t>Texto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -841,12 +988,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="6">
@@ -919,14 +1072,63 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -940,54 +1142,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1320,1757 +1478,1842 @@
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D2" s="8">
+      <c r="C2" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="4">
         <v>2023</v>
       </c>
       <c r="E2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>228</v>
+      <c r="E3" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="8" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E4" s="21"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="8" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="21"/>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="8" t="s">
+      <c r="A6" s="22"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E6" s="21"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="8" t="s">
+      <c r="A7" s="23"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E7" s="21"/>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="15" t="s">
+      <c r="C8" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E8" s="21" t="s">
-        <v>228</v>
+      <c r="E8" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="15" t="s">
+      <c r="A9" s="22"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="13"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="15" t="s">
+      <c r="A10" s="22"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="15" t="s">
+      <c r="A11" s="22"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="13"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="15" t="s">
+      <c r="A12" s="22"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="13"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="15" t="s">
+      <c r="A13" s="22"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E13" s="21"/>
+      <c r="E13" s="13"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="15" t="s">
+      <c r="A14" s="22"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="13"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="15" t="s">
+      <c r="A15" s="22"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="15" t="s">
+      <c r="A16" s="22"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="13"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="15" t="s">
+      <c r="A17" s="22"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E17" s="21"/>
+      <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="15" t="s">
+      <c r="A18" s="22"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E18" s="21"/>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="15" t="s">
+      <c r="A19" s="22"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E19" s="21"/>
+      <c r="E19" s="13"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="15" t="s">
+      <c r="A20" s="22"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E20" s="21"/>
+      <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="15" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E21" s="21"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="15" t="s">
+      <c r="A22" s="22"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E22" s="21"/>
+      <c r="E22" s="13"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="15" t="s">
+      <c r="A23" s="22"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E23" s="21"/>
+      <c r="E23" s="13"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="15" t="s">
+      <c r="A24" s="22"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E24" s="21"/>
+      <c r="E24" s="13"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="15" t="s">
+      <c r="A25" s="22"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E25" s="21"/>
+      <c r="E25" s="13"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="15" t="s">
+      <c r="A26" s="22"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E26" s="21"/>
+      <c r="E26" s="13"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="15" t="s">
+      <c r="A27" s="22"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E27" s="21"/>
+      <c r="E27" s="13"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="15" t="s">
+      <c r="A28" s="22"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E28" s="21"/>
+      <c r="E28" s="13"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="15" t="s">
+      <c r="A29" s="22"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E29" s="21"/>
+      <c r="E29" s="13"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="15" t="s">
+      <c r="A30" s="22"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="E30" s="21"/>
+      <c r="E30" s="13"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="15" t="s">
+      <c r="A31" s="22"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="E31" s="21"/>
+      <c r="E31" s="13"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="15" t="s">
+      <c r="A32" s="22"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E32" s="21"/>
+      <c r="E32" s="13"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="15" t="s">
+      <c r="A33" s="22"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E33" s="21"/>
+      <c r="E33" s="13"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="15" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E34" s="21"/>
+      <c r="E34" s="13"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>163</v>
+      <c r="C35" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="E35" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D36" s="12" t="s">
+      <c r="C36" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E36" s="21" t="s">
-        <v>228</v>
+      <c r="E36" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="12" t="s">
+      <c r="A37" s="23"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E37" s="21"/>
+      <c r="E37" s="13"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C38" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>163</v>
+      <c r="C38" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="E38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C39" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="D39" s="8" t="s">
+      <c r="C39" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="E39" s="21" t="s">
-        <v>228</v>
+      <c r="E39" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="6"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="8" t="s">
+      <c r="A40" s="24"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="E40" s="21"/>
+      <c r="E40" s="13"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="D41" s="8" t="s">
+      <c r="B41" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E41" s="21" t="s">
-        <v>228</v>
+      <c r="E41" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="6"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="8" t="s">
+      <c r="A42" s="24"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E42" s="21"/>
+      <c r="E42" s="13"/>
     </row>
     <row r="43" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>162</v>
+      <c r="B43" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E43" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E44" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C44" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="E44" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>162</v>
+      <c r="C45" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E45" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="D46" s="8" t="s">
+      <c r="C46" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E46" s="21" t="s">
-        <v>228</v>
+      <c r="E46" s="13" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="8" t="s">
+      <c r="A47" s="22"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E47" s="21"/>
+      <c r="E47" s="13"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="8" t="s">
+      <c r="A48" s="22"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E48" s="21"/>
+      <c r="E48" s="13"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="8" t="s">
+      <c r="A49" s="22"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E49" s="21"/>
+      <c r="E49" s="13"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="8" t="s">
+      <c r="A50" s="22"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E50" s="21"/>
+      <c r="E50" s="13"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="8" t="s">
+      <c r="A51" s="22"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E51" s="21"/>
+      <c r="E51" s="13"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="8" t="s">
+      <c r="A52" s="22"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E52" s="21"/>
+      <c r="E52" s="13"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="5"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="8" t="s">
+      <c r="A53" s="23"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E53" s="21"/>
+      <c r="E53" s="13"/>
     </row>
     <row r="54" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C54" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>163</v>
+      <c r="C54" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>162</v>
       </c>
       <c r="E54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C55" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>163</v>
+      <c r="C55" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>162</v>
       </c>
       <c r="E55" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D56" s="16"/>
+      <c r="C56" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D56" s="7"/>
       <c r="E56" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="C57" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>162</v>
+      <c r="B57" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="E57" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="C58" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D58" s="8"/>
+      <c r="B58" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E58" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C59" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D59" s="8"/>
+      <c r="B59" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E59" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D60" s="8"/>
+      <c r="B60" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E60" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B61" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="C61" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D61" s="8"/>
+      <c r="B61" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B62" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="C62" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D62" s="8"/>
+      <c r="B62" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E62" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B63" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="C63" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D63" s="8"/>
+      <c r="B63" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E63" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B64" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C64" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D64" s="8"/>
+      <c r="B64" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E64" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B65" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D65" s="8"/>
+      <c r="B65" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E65" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B66" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D66" s="8"/>
+      <c r="B66" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E66" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D67" s="8"/>
+      <c r="B67" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E67" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="C68" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D68" s="8"/>
+      <c r="B68" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E68" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="C69" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D69" s="8"/>
+      <c r="B69" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E69" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B70" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C70" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D70" s="8"/>
+      <c r="B70" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E70" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B71" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C71" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D71" s="8"/>
+      <c r="B71" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E71" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B72" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="C72" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D72" s="8"/>
+      <c r="B72" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E72" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B73" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C73" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D73" s="8"/>
+      <c r="B73" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E73" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B74" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C74" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D74" s="8"/>
+      <c r="B74" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E74" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B75" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C75" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D75" s="8"/>
+      <c r="B75" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E75" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B76" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="C76" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D76" s="8"/>
+      <c r="B76" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E76" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B77" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="C77" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D77" s="8"/>
+      <c r="B77" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E77" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C78" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D78" s="8"/>
+      <c r="C78" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D78" s="4"/>
       <c r="E78" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C79" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D79" s="8"/>
+      <c r="C79" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D79" s="4"/>
       <c r="E79" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C80" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D80" s="16"/>
+      <c r="C80" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D80" s="7"/>
       <c r="E80" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B81" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="C81" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D81" s="8"/>
+      <c r="B81" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E81" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B82" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="C82" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D82" s="8"/>
+      <c r="B82" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E82" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B83" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="C83" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D83" s="8"/>
+      <c r="B83" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E83" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B84" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="C84" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D84" s="8"/>
+      <c r="B84" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E84" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B85" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C85" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D85" s="8"/>
+      <c r="B85" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E85" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B86" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="C86" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D86" s="8"/>
+      <c r="B86" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E86" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B87" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="C87" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D87" s="8"/>
+      <c r="B87" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E87" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B88" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C88" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D88" s="8"/>
+      <c r="B88" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E88" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B89" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="C89" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D89" s="8"/>
+      <c r="B89" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E89" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B90" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="C90" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D90" s="8"/>
+      <c r="B90" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E90" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B91" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C91" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D91" s="8"/>
+      <c r="B91" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E91" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B92" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C92" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D92" s="8"/>
+      <c r="B92" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B93" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="C93" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D93" s="8"/>
+      <c r="B93" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E93" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B94" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C94" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D94" s="8"/>
+      <c r="B94" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E94" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B95" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="C95" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D95" s="8"/>
+      <c r="B95" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E95" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B96" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="C96" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D96" s="8"/>
+      <c r="B96" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E96" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B97" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C97" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D97" s="8"/>
+      <c r="B97" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E97" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B98" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="C98" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D98" s="8"/>
+      <c r="B98" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E98" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B99" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="C99" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D99" s="8"/>
+      <c r="B99" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E99" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C100" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D100" s="8"/>
+      <c r="C100" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D100" s="4"/>
       <c r="E100" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C101" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D101" s="8"/>
+      <c r="C101" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D101" s="4"/>
       <c r="E101" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C102" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D102" s="8"/>
+      <c r="C102" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D102" s="4"/>
       <c r="E102" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B103" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="C103" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D103" s="8" t="s">
-        <v>162</v>
+      <c r="B103" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E103" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B104" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="C104" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D104" s="8" t="s">
-        <v>162</v>
+      <c r="B104" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E104" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B105" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="C105" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D105" s="8" t="s">
-        <v>162</v>
+      <c r="B105" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E105" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B106" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="C106" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D106" s="8" t="s">
-        <v>162</v>
+      <c r="B106" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E106" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B107" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="C107" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D107" s="8" t="s">
-        <v>162</v>
+      <c r="B107" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E107" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B108" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C108" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D108" s="8" t="s">
-        <v>162</v>
+      <c r="B108" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E108" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B109" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C109" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D109" s="8" t="s">
-        <v>162</v>
+      <c r="B109" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E109" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B110" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="C110" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D110" s="8" t="s">
-        <v>162</v>
+      <c r="B110" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E110" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B111" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="C111" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D111" s="8" t="s">
-        <v>162</v>
+      <c r="B111" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E111" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B112" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C112" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D112" s="8" t="s">
-        <v>162</v>
+      <c r="B112" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E112" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B113" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="C113" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>162</v>
+      <c r="B113" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E113" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B114" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="C114" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>162</v>
+      <c r="B114" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E114" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B115" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="C115" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D115" s="8" t="s">
-        <v>162</v>
+      <c r="B115" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E115" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B116" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="C116" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D116" s="8" t="s">
-        <v>162</v>
+      <c r="B116" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E116" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B117" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D117" s="8" t="s">
-        <v>162</v>
+      <c r="B117" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E117" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B118" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="C118" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D118" s="8" t="s">
-        <v>162</v>
+      <c r="B118" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E118" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B119" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="C119" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D119" s="8" t="s">
-        <v>162</v>
+      <c r="B119" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E119" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B120" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C120" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D120" s="8" t="s">
-        <v>162</v>
+      <c r="B120" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E120" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B121" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="C121" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D121" s="8" t="s">
-        <v>162</v>
+      <c r="B121" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E121" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B122" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="C122" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D122" s="8" t="s">
-        <v>162</v>
+      <c r="B122" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="E122" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B123" s="8" t="s">
+      <c r="B123" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C123" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D123" s="8" t="s">
-        <v>227</v>
+      <c r="C123" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="E123" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B124" s="8" t="s">
+      <c r="B124" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C124" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D124" s="8" t="s">
-        <v>227</v>
+      <c r="C124" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="E124" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B125" s="8" t="s">
+      <c r="B125" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C125" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D125" s="8" t="s">
-        <v>227</v>
+      <c r="C125" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="E125" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B126" s="8" t="s">
+      <c r="B126" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C126" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D126" s="8" t="s">
-        <v>227</v>
+      <c r="C126" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="E126" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B127" s="8" t="s">
+      <c r="B127" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C127" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D127" s="8" t="s">
-        <v>227</v>
+      <c r="C127" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="E127" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B128" s="8" t="s">
+      <c r="B128" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C128" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D128" s="8" t="s">
-        <v>227</v>
+      <c r="C128" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="E128" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <mergeCells count="24">
-    <mergeCell ref="E8:E34"/>
-    <mergeCell ref="E3:E7"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A34"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A46:A53"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B34"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
     <mergeCell ref="E46:E53"/>
     <mergeCell ref="C3:C7"/>
     <mergeCell ref="C8:C34"/>
@@ -3078,20 +3321,192 @@
     <mergeCell ref="C39:C40"/>
     <mergeCell ref="C41:C42"/>
     <mergeCell ref="C46:C53"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B8:B34"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B46:B53"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A34"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A46:A53"/>
+    <mergeCell ref="E8:E34"/>
+    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="E41:E42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="180.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="B5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>